--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487791_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487791_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1176</v>
+        <v>7.5989</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4841</v>
+        <v>7.9361</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3665</v>
+        <v>-0.3371</v>
       </c>
       <c r="G2" t="n">
         <v>3.6448</v>
@@ -610,13 +610,13 @@
         <v>3.538</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8859</v>
+        <v>1.3672</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9283</v>
+        <v>1.3802</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0424</v>
+        <v>-0.013</v>
       </c>
       <c r="V2" t="n">
         <v>-0.743</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6425</v>
+        <v>1.1923</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0611</v>
+        <v>0.8219</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4186</v>
+        <v>0.3704</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1494</v>
+        <v>0.4698</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2367</v>
+        <v>-2.1452</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08740000000000001</v>
+        <v>2.615</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9774</v>
+        <v>1.6456</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8207</v>
+        <v>-0.8959</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1568</v>
+        <v>2.5415</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1268</v>
+        <v>-1.1758</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0574</v>
+        <v>-1.2493</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0694</v>
+        <v>0.0735</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8325</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6244</v>
+        <v>0.1086</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5219</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1024</v>
+        <v>0.0405</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5838</v>
+        <v>1.2383</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8137</v>
+        <v>1.3975</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.23</v>
+        <v>-0.1592</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5494</v>
+        <v>1.1783</v>
       </c>
       <c r="E4" t="n">
-        <v>0.179</v>
+        <v>1.5969</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3704</v>
+        <v>-0.4186</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4698</v>
+        <v>-0.1494</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1452</v>
+        <v>-0.2367</v>
       </c>
       <c r="I4" t="n">
-        <v>2.615</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6456</v>
+        <v>0.9774</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8959</v>
+        <v>0.8207</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5415</v>
+        <v>0.1568</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1758</v>
+        <v>-1.1268</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2493</v>
+        <v>-1.0574</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0735</v>
+        <v>-0.0694</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5343</v>
+        <v>-0.0886</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5748</v>
+        <v>0.0138</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0405</v>
+        <v>-0.1024</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2383</v>
+        <v>0.5838</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3975</v>
+        <v>0.8137</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1592</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2766</v>
+        <v>-0.917</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6221</v>
+        <v>-0.0745</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3455</v>
+        <v>-0.8425</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2725</v>
+        <v>-4.0931</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6569</v>
+        <v>-3.0382</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6156</v>
+        <v>-1.0548</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1167</v>
+        <v>-2.0924</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0377</v>
+        <v>-0.3926</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1544</v>
+        <v>-1.6998</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1558</v>
+        <v>-2.0007</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.6946</v>
+        <v>-2.6456</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5389</v>
+        <v>0.645</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.8325</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1218</v>
+        <v>2.9137</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6919</v>
+        <v>0.3376</v>
       </c>
       <c r="T5" t="n">
-        <v>4.6306</v>
+        <v>1.534</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9388</v>
+        <v>-1.1965</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1428</v>
+        <v>2.006</v>
       </c>
       <c r="W5" t="n">
-        <v>0.23</v>
+        <v>2.565</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3727</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0053</v>
+        <v>-1.2429</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8666</v>
+        <v>-1.665</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8718</v>
+        <v>0.4221</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.0931</v>
+        <v>-2.125</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.0382</v>
+        <v>-1.8229</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0548</v>
+        <v>-0.3021</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.0924</v>
+        <v>-1.1369</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3926</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.6998</v>
+        <v>-0.5184</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0007</v>
+        <v>-0.9881</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.6456</v>
+        <v>-1.2044</v>
       </c>
       <c r="O6" t="n">
-        <v>0.645</v>
+        <v>0.2164</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0812</v>
+        <v>-1.2487</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9137</v>
+        <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2493</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4751</v>
+        <v>0.4906</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2258</v>
+        <v>0.2075</v>
       </c>
       <c r="V6" t="n">
-        <v>2.006</v>
+        <v>0.184</v>
       </c>
       <c r="W6" t="n">
-        <v>2.565</v>
+        <v>0.23</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.046</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6088</v>
+        <v>-2.194</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2364</v>
+        <v>-0.8192</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6276</v>
+        <v>-1.3749</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.125</v>
+        <v>-2.2725</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8229</v>
+        <v>-1.6569</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3021</v>
+        <v>-0.6156</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1369</v>
+        <v>-0.1167</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6183999999999999</v>
+        <v>1.0377</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5184</v>
+        <v>-1.1544</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9881</v>
+        <v>-2.1558</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2044</v>
+        <v>-2.6946</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2164</v>
+        <v>0.5389</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2487</v>
+        <v>-3.1218</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2487</v>
+        <v>3.1218</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3322</v>
+        <v>1.2213</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9192</v>
+        <v>2.1894</v>
       </c>
       <c r="U7" t="n">
-        <v>0.413</v>
+        <v>-0.9681</v>
       </c>
       <c r="V7" t="n">
-        <v>0.184</v>
+        <v>-1.1428</v>
       </c>
       <c r="W7" t="n">
         <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.046</v>
+        <v>-1.3727</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.1819</v>
+        <v>-3.4509</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.6023</v>
+        <v>-2.9594</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5795</v>
+        <v>-0.4914</v>
       </c>
       <c r="G8" t="n">
         <v>-3.5882</v>
@@ -1078,13 +1078,13 @@
         <v>2.0812</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3856</v>
+        <v>0.3454</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0867</v>
+        <v>0.7297</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4723</v>
+        <v>-0.3842</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.0255</v>
+        <v>-3.6473</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9353</v>
+        <v>-1.7333</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0902</v>
+        <v>-1.914</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3299</v>
@@ -1156,13 +1156,13 @@
         <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5227</v>
+        <v>-0.1445</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7829</v>
+        <v>0.4191</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7398</v>
+        <v>-0.5637</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7973</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1007</v>
+        <v>-4.2011</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.5548</v>
+        <v>-4.567</v>
       </c>
       <c r="F10" t="n">
-        <v>0.454</v>
+        <v>0.3659</v>
       </c>
       <c r="G10" t="n">
         <v>-4.7437</v>
@@ -1234,13 +1234,13 @@
         <v>2.4974</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8012</v>
+        <v>0.0985</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2519</v>
+        <v>0.7358</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5493</v>
+        <v>-0.6374</v>
       </c>
       <c r="V10" t="n">
         <v>1.0685</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3361</v>
+        <v>-5.6837</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1159</v>
+        <v>-1.463500000000002</v>
       </c>
       <c r="F11" t="n">
         <v>-4.2201</v>
@@ -1282,16 +1282,16 @@
         <v>-21.0448</v>
       </c>
       <c r="I11" t="n">
-        <v>5.8579</v>
+        <v>5.857900000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5091999999999999</v>
+        <v>-0.5092000000000003</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.488900000000001</v>
+        <v>-3.4889</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9799</v>
+        <v>2.979899999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-14.678</v>
@@ -1312,10 +1312,10 @@
         <v>19.7712</v>
       </c>
       <c r="S11" t="n">
-        <v>3.291100000000001</v>
+        <v>3.9436</v>
       </c>
       <c r="T11" t="n">
-        <v>6.908399999999999</v>
+        <v>7.560700000000001</v>
       </c>
       <c r="U11" t="n">
         <v>-3.6173</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.4197</v>
+        <v>3.3991</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6994</v>
+        <v>3.3981</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7203</v>
+        <v>0.001</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7879</v>
+        <v>2.3274</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5562</v>
+        <v>2.9617</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7682</v>
+        <v>-0.6343</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7309</v>
+        <v>2.6296</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3277</v>
+        <v>2.5904</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5968</v>
+        <v>0.0392</v>
       </c>
       <c r="M12" t="n">
-        <v>0.057</v>
+        <v>-0.3022</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2284</v>
+        <v>0.3713</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1714</v>
+        <v>-0.6735</v>
       </c>
       <c r="P12" t="n">
         <v>0.2081</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2893</v>
+        <v>1.2487</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0074</v>
+        <v>0.8636</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0497</v>
+        <v>0.9954</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0423</v>
+        <v>-0.1317</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5838</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4221</v>
+        <v>3.1563</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5053</v>
+        <v>2.0565</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.08309999999999999</v>
+        <v>1.0998</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3274</v>
+        <v>3.7879</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9617</v>
+        <v>4.5562</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6343</v>
+        <v>-0.7682</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6296</v>
+        <v>3.7309</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5904</v>
+        <v>4.3277</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0392</v>
+        <v>-0.5968</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3022</v>
+        <v>0.057</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3713</v>
+        <v>0.2284</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6735</v>
+        <v>-0.1714</v>
       </c>
       <c r="P13" t="n">
         <v>0.2081</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2487</v>
+        <v>2.2893</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8866000000000001</v>
+        <v>-0.256</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1025</v>
+        <v>0.4067</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2159</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V13" t="n">
+        <v>-0.5838</v>
+      </c>
+      <c r="W13" t="n">
         <v>0</v>
       </c>
-      <c r="W13" t="n">
-        <v>0.8137</v>
-      </c>
       <c r="X13" t="n">
-        <v>-0.8137</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2183</v>
+        <v>3.0001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5319</v>
+        <v>2.3176</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6864</v>
+        <v>0.6824</v>
       </c>
       <c r="G14" t="n">
         <v>3.3189</v>
@@ -1546,13 +1546,13 @@
         <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1193</v>
+        <v>-0.3376</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3229</v>
+        <v>0.1086</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4423</v>
+        <v>-0.4462</v>
       </c>
       <c r="V14" t="n">
         <v>-0.8137</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1028</v>
+        <v>2.582</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3011</v>
+        <v>3.4413</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1984</v>
+        <v>-0.8593</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5944</v>
+        <v>6.054</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8041</v>
+        <v>6.7161</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7903</v>
+        <v>-0.6621</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4067</v>
+        <v>5.7316</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1919</v>
+        <v>5.8672</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2148</v>
+        <v>-0.1355</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1877</v>
+        <v>0.3224</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6122</v>
+        <v>0.849</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4245</v>
+        <v>-0.5266</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6244</v>
+        <v>-3.7461</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2081</v>
+        <v>-5.4111</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4678</v>
+        <v>-1.1234</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1025</v>
+        <v>-0.0281</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6348</v>
+        <v>-1.0953</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5838</v>
+        <v>1.3975</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.1488</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5838</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0144</v>
+        <v>2.1693</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0127</v>
+        <v>1.8725</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9982</v>
+        <v>0.2968</v>
       </c>
       <c r="G16" t="n">
-        <v>6.054</v>
+        <v>1.5944</v>
       </c>
       <c r="H16" t="n">
-        <v>6.7161</v>
+        <v>0.8041</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6621</v>
+        <v>0.7903</v>
       </c>
       <c r="J16" t="n">
-        <v>5.7316</v>
+        <v>1.4067</v>
       </c>
       <c r="K16" t="n">
-        <v>5.8672</v>
+        <v>0.1919</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1355</v>
+        <v>1.2148</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3224</v>
+        <v>0.1877</v>
       </c>
       <c r="N16" t="n">
-        <v>0.849</v>
+        <v>0.6122</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5266</v>
+        <v>-0.4245</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.7461</v>
+        <v>0.6244</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.4111</v>
+        <v>-0.2081</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.691</v>
+        <v>0.5343</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4567</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2343</v>
+        <v>-0.1396</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3975</v>
+        <v>-0.5838</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1488</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7513</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5181</v>
+        <v>0.6625</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3063</v>
+        <v>-1.6278</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8244</v>
+        <v>2.2902</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1041</v>
@@ -1780,13 +1780,13 @@
         <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3953</v>
+        <v>0.5397</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1802</v>
+        <v>0.8587</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-0.319</v>
       </c>
       <c r="V17" t="n">
         <v>-0.23</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8759</v>
+        <v>-0.5456</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0815</v>
+        <v>-0.5457</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2056</v>
+        <v>0.0001</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3818</v>
@@ -1858,13 +1858,13 @@
         <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2642</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3138</v>
+        <v>0.222</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0496</v>
+        <v>-0.1559</v>
       </c>
       <c r="V18" t="n">
         <v>-0.23</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0401</v>
+        <v>-0.748</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8079</v>
+        <v>-1.4864</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7677</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4491</v>
@@ -1936,13 +1936,13 @@
         <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0333</v>
+        <v>0.3254</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1305</v>
+        <v>0.191</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1638</v>
+        <v>0.1344</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6277</v>
+        <v>-1.1047</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0015</v>
+        <v>-0.68</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6262</v>
+        <v>-0.4247</v>
       </c>
       <c r="G20" t="n">
         <v>0.8869</v>
@@ -2014,13 +2014,13 @@
         <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5573</v>
+        <v>-1.0342</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3915</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1658</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0.7076</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2801</v>
+        <v>-1.827</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5702</v>
+        <v>-0.7845</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7099</v>
+        <v>-1.0425</v>
       </c>
       <c r="G21" t="n">
         <v>0.456</v>
@@ -2092,13 +2092,13 @@
         <v>1.8731</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8391</v>
+        <v>-1.386</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3353</v>
+        <v>0.121</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.1744</v>
+        <v>-1.507</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5213</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5354</v>
+        <v>-2.979</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0629</v>
+        <v>-3.7414</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5275</v>
+        <v>0.7624</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3035</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6106</v>
+        <v>-0.0543</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1833</v>
+        <v>0.1381</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4273</v>
+        <v>-0.1924</v>
       </c>
       <c r="V22" t="n">
         <v>0.4599</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.336199999999997</v>
+        <v>7.765</v>
       </c>
       <c r="E23" t="n">
-        <v>4.220100000000001</v>
+        <v>4.2202</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1161</v>
+        <v>3.5446</v>
       </c>
       <c r="G23" t="n">
         <v>15.187</v>
@@ -2218,7 +2218,7 @@
         <v>21.0449</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.857600000000001</v>
+        <v>-5.8576</v>
       </c>
       <c r="J23" t="n">
         <v>14.6778</v>
@@ -2227,7 +2227,7 @@
         <v>17.55599999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.8779</v>
+        <v>-2.877899999999999</v>
       </c>
       <c r="M23" t="n">
         <v>0.5091000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>15.6088</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.2911</v>
+        <v>-1.8624</v>
       </c>
       <c r="T23" t="n">
         <v>3.6173</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.908499999999999</v>
+        <v>-5.4797</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3976</v>
